--- a/portal/ict/dtr/assets/Master DTR Template.xlsx
+++ b/portal/ict/dtr/assets/Master DTR Template.xlsx
@@ -3488,7 +3488,9 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="38"/>
-      <c r="B46" s="39"/>
+      <c r="B46" s="39" t="s">
+        <v>48</v>
+      </c>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
       <c r="E46" s="40"/>

--- a/portal/ict/dtr/assets/Master DTR Template.xlsx
+++ b/portal/ict/dtr/assets/Master DTR Template.xlsx
@@ -2463,6 +2463,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2117BD85-EC4B-4E8F-BBA4-23CE6EAF8BC7}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Q55"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3709,7 +3712,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="5" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="14" orientation="portrait" horizontalDpi="0" verticalDpi="0" fitToWidth="1" fitToHeight="1" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/portal/ict/dtr/assets/Master DTR Template.xlsx
+++ b/portal/ict/dtr/assets/Master DTR Template.xlsx
@@ -2463,9 +2463,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2117BD85-EC4B-4E8F-BBA4-23CE6EAF8BC7}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:Q55"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3712,7 +3709,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="14" orientation="portrait" horizontalDpi="0" verticalDpi="0" fitToWidth="1" fitToHeight="1" r:id="rId1"/>
+  <pageSetup paperSize="5" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>